--- a/Assignment-1/ODI-2026-cleaned.xlsx
+++ b/Assignment-1/ODI-2026-cleaned.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1345,7 +1345,7 @@
         <v>25</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>27</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="b">
         <v>1</v>
@@ -2052,7 +2052,7 @@
         <v>26</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -2961,7 +2961,7 @@
         <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="b">
         <v>1</v>
@@ -3365,7 +3365,7 @@
         <v>24</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>23</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" t="b">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>25</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="b">
         <v>0</v>
@@ -4779,7 +4779,7 @@
         <v>27</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="b">
         <v>0</v>
@@ -6900,7 +6900,7 @@
         <v>25</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U64" t="b">
         <v>1</v>
@@ -7203,7 +7203,7 @@
         <v>25</v>
       </c>
       <c r="T67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U67" t="b">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>25</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="b">
         <v>1</v>
@@ -8011,7 +8011,7 @@
         <v>25</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U75" t="b">
         <v>1</v>
@@ -8112,7 +8112,7 @@
         <v>25</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U76" t="b">
         <v>0</v>
@@ -8314,7 +8314,7 @@
         <v>25</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U78" t="b">
         <v>0</v>
@@ -8415,7 +8415,7 @@
         <v>26</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U79" t="b">
         <v>0</v>
@@ -8516,7 +8516,7 @@
         <v>25</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
@@ -8617,7 +8617,7 @@
         <v>25</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U81" t="b">
         <v>0</v>
@@ -8920,7 +8920,7 @@
         <v>22</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U84" t="b">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         <v>26</v>
       </c>
       <c r="T88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U88" t="b">
         <v>0</v>
@@ -9627,7 +9627,7 @@
         <v>25</v>
       </c>
       <c r="T91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U91" t="b">
         <v>0</v>
@@ -10031,7 +10031,7 @@
         <v>22</v>
       </c>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U95" t="b">
         <v>0</v>
@@ -10132,7 +10132,7 @@
         <v>25</v>
       </c>
       <c r="T96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U96" t="b">
         <v>0</v>
@@ -12960,7 +12960,7 @@
         <v>24</v>
       </c>
       <c r="T124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U124" t="b">
         <v>1</v>
@@ -13061,7 +13061,7 @@
         <v>25</v>
       </c>
       <c r="T125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U125" t="b">
         <v>1</v>
@@ -13970,7 +13970,7 @@
         <v>22</v>
       </c>
       <c r="T134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U134" t="b">
         <v>1</v>
@@ -14273,7 +14273,7 @@
         <v>23</v>
       </c>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" t="b">
         <v>1</v>
@@ -14374,7 +14374,7 @@
         <v>32</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U138" t="b">
         <v>1</v>
@@ -16091,7 +16091,7 @@
         <v>25</v>
       </c>
       <c r="T155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U155" t="b">
         <v>1</v>
